--- a/artfynd/A 22209-2025 artfynd.xlsx
+++ b/artfynd/A 22209-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1152,6 +1152,1961 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126117443</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91528</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>658</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>605449</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7017035</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126117456</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>605356</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7017178</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126117446</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91528</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>658</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>605337</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7017190</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126117452</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>605358</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7017186</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126117428</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91232</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>605442</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7017113</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126117450</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>605356</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7017183</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126117454</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91228</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>605372</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7017035</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126117442</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91528</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>658</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>605492</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7017148</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126117431</v>
+      </c>
+      <c r="B14" t="n">
+        <v>4772</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>605393</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7017189</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126117445</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91528</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>658</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>605242</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7017164</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126117449</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>605348</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7017068</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126117429</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91232</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>605445</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7017046</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126117427</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91197</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>605225</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7017157</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126117426</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5196</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>605393</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7017189</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126117455</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91250</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>605403</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7017171</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126117457</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>605367</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7017177</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126117444</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91528</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>658</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>605225</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7017164</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126117440</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98360</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>605358</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7017058</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126117430</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91232</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>605397</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7017190</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126117451</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>605345</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7017186</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22209-2025 artfynd.xlsx
+++ b/artfynd/A 22209-2025 artfynd.xlsx
@@ -1154,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126117443</v>
+        <v>126117456</v>
       </c>
       <c r="B6" t="n">
-        <v>91528</v>
+        <v>78972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,21 +1165,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>605449</v>
+        <v>605356</v>
       </c>
       <c r="R6" t="n">
-        <v>7017035</v>
+        <v>7017178</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1225,6 +1225,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126117456</v>
+        <v>126117443</v>
       </c>
       <c r="B7" t="n">
-        <v>78972</v>
+        <v>91528</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,21 +1267,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1286,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>605356</v>
+        <v>605449</v>
       </c>
       <c r="R7" t="n">
-        <v>7017178</v>
+        <v>7017035</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1322,11 +1327,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1741,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126117454</v>
+        <v>126117442</v>
       </c>
       <c r="B12" t="n">
-        <v>91228</v>
+        <v>91528</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1752,21 +1752,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>605372</v>
+        <v>605492</v>
       </c>
       <c r="R12" t="n">
-        <v>7017035</v>
+        <v>7017148</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1838,10 +1838,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126117442</v>
+        <v>126117454</v>
       </c>
       <c r="B13" t="n">
-        <v>91528</v>
+        <v>91228</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1849,21 +1849,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>605492</v>
+        <v>605372</v>
       </c>
       <c r="R13" t="n">
-        <v>7017148</v>
+        <v>7017035</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2425,32 +2425,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126117426</v>
+        <v>126117455</v>
       </c>
       <c r="B19" t="n">
-        <v>5196</v>
+        <v>91250</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105930</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2460,10 +2460,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>605393</v>
+        <v>605403</v>
       </c>
       <c r="R19" t="n">
-        <v>7017189</v>
+        <v>7017171</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2496,11 +2496,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2527,32 +2522,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126117455</v>
+        <v>126117426</v>
       </c>
       <c r="B20" t="n">
-        <v>91250</v>
+        <v>5196</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2562,10 +2557,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>605403</v>
+        <v>605393</v>
       </c>
       <c r="R20" t="n">
-        <v>7017171</v>
+        <v>7017189</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2598,6 +2593,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2818,32 +2818,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126117440</v>
+        <v>126117430</v>
       </c>
       <c r="B23" t="n">
-        <v>98360</v>
+        <v>91232</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>605358</v>
+        <v>605397</v>
       </c>
       <c r="R23" t="n">
-        <v>7017058</v>
+        <v>7017190</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2915,32 +2915,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126117430</v>
+        <v>126117440</v>
       </c>
       <c r="B24" t="n">
-        <v>91232</v>
+        <v>98360</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>605397</v>
+        <v>605358</v>
       </c>
       <c r="R24" t="n">
-        <v>7017190</v>
+        <v>7017058</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>

--- a/artfynd/A 22209-2025 artfynd.xlsx
+++ b/artfynd/A 22209-2025 artfynd.xlsx
@@ -1353,32 +1353,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126117446</v>
+        <v>126117452</v>
       </c>
       <c r="B8" t="n">
-        <v>91528</v>
+        <v>98339</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>605337</v>
+        <v>605358</v>
       </c>
       <c r="R8" t="n">
-        <v>7017190</v>
+        <v>7017186</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1450,32 +1450,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126117452</v>
+        <v>126117446</v>
       </c>
       <c r="B9" t="n">
-        <v>98339</v>
+        <v>91528</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>605358</v>
+        <v>605337</v>
       </c>
       <c r="R9" t="n">
-        <v>7017186</v>
+        <v>7017190</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 22209-2025 artfynd.xlsx
+++ b/artfynd/A 22209-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1157,7 +1157,7 @@
         <v>126117456</v>
       </c>
       <c r="B6" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>126117443</v>
       </c>
       <c r="B7" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,32 +1353,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126117452</v>
+        <v>126117446</v>
       </c>
       <c r="B8" t="n">
-        <v>98339</v>
+        <v>91530</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>605358</v>
+        <v>605337</v>
       </c>
       <c r="R8" t="n">
-        <v>7017186</v>
+        <v>7017190</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1450,32 +1450,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126117446</v>
+        <v>126117452</v>
       </c>
       <c r="B9" t="n">
-        <v>91528</v>
+        <v>98341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>605337</v>
+        <v>605358</v>
       </c>
       <c r="R9" t="n">
-        <v>7017190</v>
+        <v>7017186</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1550,7 +1550,7 @@
         <v>126117428</v>
       </c>
       <c r="B10" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>126117450</v>
       </c>
       <c r="B11" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>126117442</v>
       </c>
       <c r="B12" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>126117454</v>
       </c>
       <c r="B13" t="n">
-        <v>91228</v>
+        <v>91230</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>126117445</v>
       </c>
       <c r="B15" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>126117449</v>
       </c>
       <c r="B16" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>126117429</v>
       </c>
       <c r="B17" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>126117427</v>
       </c>
       <c r="B18" t="n">
-        <v>91197</v>
+        <v>91199</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>126117455</v>
       </c>
       <c r="B19" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>126117457</v>
       </c>
       <c r="B21" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>126117444</v>
       </c>
       <c r="B22" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>126117430</v>
       </c>
       <c r="B23" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>126117440</v>
       </c>
       <c r="B24" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>126117451</v>
       </c>
       <c r="B25" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3106,6 +3106,108 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126117460</v>
+      </c>
+      <c r="B26" t="n">
+        <v>5176</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>605391</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7017189</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22209-2025 artfynd.xlsx
+++ b/artfynd/A 22209-2025 artfynd.xlsx
@@ -1353,32 +1353,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126117446</v>
+        <v>126117452</v>
       </c>
       <c r="B8" t="n">
-        <v>91530</v>
+        <v>98341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>605337</v>
+        <v>605358</v>
       </c>
       <c r="R8" t="n">
-        <v>7017190</v>
+        <v>7017186</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1450,32 +1450,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126117452</v>
+        <v>126117446</v>
       </c>
       <c r="B9" t="n">
-        <v>98341</v>
+        <v>91530</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>605358</v>
+        <v>605337</v>
       </c>
       <c r="R9" t="n">
-        <v>7017186</v>
+        <v>7017190</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 22209-2025 artfynd.xlsx
+++ b/artfynd/A 22209-2025 artfynd.xlsx
@@ -1154,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126117456</v>
+        <v>126117443</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>91532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,21 +1165,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>605356</v>
+        <v>605449</v>
       </c>
       <c r="R6" t="n">
-        <v>7017178</v>
+        <v>7017035</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1225,11 +1225,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126117443</v>
+        <v>126117456</v>
       </c>
       <c r="B7" t="n">
-        <v>91530</v>
+        <v>78973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,21 +1262,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1291,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>605449</v>
+        <v>605356</v>
       </c>
       <c r="R7" t="n">
-        <v>7017035</v>
+        <v>7017178</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1327,6 +1322,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,7 +1356,7 @@
         <v>126117452</v>
       </c>
       <c r="B8" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>126117446</v>
       </c>
       <c r="B9" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>126117428</v>
       </c>
       <c r="B10" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>126117450</v>
       </c>
       <c r="B11" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>126117442</v>
       </c>
       <c r="B12" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>126117454</v>
       </c>
       <c r="B13" t="n">
-        <v>91230</v>
+        <v>91232</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>126117445</v>
       </c>
       <c r="B15" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>126117449</v>
       </c>
       <c r="B16" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>126117429</v>
       </c>
       <c r="B17" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>126117427</v>
       </c>
       <c r="B18" t="n">
-        <v>91199</v>
+        <v>91201</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>126117455</v>
       </c>
       <c r="B19" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>126117444</v>
       </c>
       <c r="B22" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>126117430</v>
       </c>
       <c r="B23" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>126117440</v>
       </c>
       <c r="B24" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>126117451</v>
       </c>
       <c r="B25" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 22209-2025 artfynd.xlsx
+++ b/artfynd/A 22209-2025 artfynd.xlsx
@@ -1154,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126117443</v>
+        <v>126117456</v>
       </c>
       <c r="B6" t="n">
-        <v>91532</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,21 +1165,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>605449</v>
+        <v>605356</v>
       </c>
       <c r="R6" t="n">
-        <v>7017035</v>
+        <v>7017178</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1225,6 +1225,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126117456</v>
+        <v>126117443</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>91532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,21 +1267,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1286,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>605356</v>
+        <v>605449</v>
       </c>
       <c r="R7" t="n">
-        <v>7017178</v>
+        <v>7017035</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1322,11 +1327,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 22209-2025 artfynd.xlsx
+++ b/artfynd/A 22209-2025 artfynd.xlsx
@@ -1154,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126117456</v>
+        <v>126117443</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>91534</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,21 +1165,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>605356</v>
+        <v>605449</v>
       </c>
       <c r="R6" t="n">
-        <v>7017178</v>
+        <v>7017035</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1225,11 +1225,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126117443</v>
+        <v>126117456</v>
       </c>
       <c r="B7" t="n">
-        <v>91532</v>
+        <v>78973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,21 +1262,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1291,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>605449</v>
+        <v>605356</v>
       </c>
       <c r="R7" t="n">
-        <v>7017035</v>
+        <v>7017178</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1327,6 +1322,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,32 +1353,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126117452</v>
+        <v>126117446</v>
       </c>
       <c r="B8" t="n">
-        <v>98343</v>
+        <v>91534</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>605358</v>
+        <v>605337</v>
       </c>
       <c r="R8" t="n">
-        <v>7017186</v>
+        <v>7017190</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1450,32 +1450,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126117446</v>
+        <v>126117452</v>
       </c>
       <c r="B9" t="n">
-        <v>91532</v>
+        <v>98345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>605337</v>
+        <v>605358</v>
       </c>
       <c r="R9" t="n">
-        <v>7017190</v>
+        <v>7017186</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1550,7 +1550,7 @@
         <v>126117428</v>
       </c>
       <c r="B10" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>126117450</v>
       </c>
       <c r="B11" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>126117442</v>
       </c>
       <c r="B12" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>126117454</v>
       </c>
       <c r="B13" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>126117445</v>
       </c>
       <c r="B15" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>126117449</v>
       </c>
       <c r="B16" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>126117429</v>
       </c>
       <c r="B17" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>126117427</v>
       </c>
       <c r="B18" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2425,32 +2425,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126117455</v>
+        <v>126117426</v>
       </c>
       <c r="B19" t="n">
-        <v>91254</v>
+        <v>5196</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>105930</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2460,10 +2460,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>605403</v>
+        <v>605393</v>
       </c>
       <c r="R19" t="n">
-        <v>7017171</v>
+        <v>7017189</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2496,6 +2496,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2522,32 +2527,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126117426</v>
+        <v>126117455</v>
       </c>
       <c r="B20" t="n">
-        <v>5196</v>
+        <v>91256</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105930</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2557,10 +2562,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>605393</v>
+        <v>605403</v>
       </c>
       <c r="R20" t="n">
-        <v>7017189</v>
+        <v>7017171</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2593,11 +2598,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2724,7 +2724,7 @@
         <v>126117444</v>
       </c>
       <c r="B22" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>126117430</v>
       </c>
       <c r="B23" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>126117440</v>
       </c>
       <c r="B24" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>126117451</v>
       </c>
       <c r="B25" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 22209-2025 artfynd.xlsx
+++ b/artfynd/A 22209-2025 artfynd.xlsx
@@ -1353,32 +1353,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126117446</v>
+        <v>126117452</v>
       </c>
       <c r="B8" t="n">
-        <v>91534</v>
+        <v>98345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>605337</v>
+        <v>605358</v>
       </c>
       <c r="R8" t="n">
-        <v>7017190</v>
+        <v>7017186</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1450,32 +1450,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126117452</v>
+        <v>126117446</v>
       </c>
       <c r="B9" t="n">
-        <v>98345</v>
+        <v>91534</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>605358</v>
+        <v>605337</v>
       </c>
       <c r="R9" t="n">
-        <v>7017186</v>
+        <v>7017190</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 22209-2025 artfynd.xlsx
+++ b/artfynd/A 22209-2025 artfynd.xlsx
@@ -1154,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126117443</v>
+        <v>126117456</v>
       </c>
       <c r="B6" t="n">
-        <v>91534</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,21 +1165,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>605449</v>
+        <v>605356</v>
       </c>
       <c r="R6" t="n">
-        <v>7017035</v>
+        <v>7017178</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1225,6 +1225,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126117456</v>
+        <v>126117443</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>91538</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,21 +1267,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1286,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>605356</v>
+        <v>605449</v>
       </c>
       <c r="R7" t="n">
-        <v>7017178</v>
+        <v>7017035</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1322,11 +1327,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,32 +1353,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126117452</v>
+        <v>126117446</v>
       </c>
       <c r="B8" t="n">
-        <v>98345</v>
+        <v>91538</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>605358</v>
+        <v>605337</v>
       </c>
       <c r="R8" t="n">
-        <v>7017186</v>
+        <v>7017190</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1450,32 +1450,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126117446</v>
+        <v>126117452</v>
       </c>
       <c r="B9" t="n">
-        <v>91534</v>
+        <v>98349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>605337</v>
+        <v>605358</v>
       </c>
       <c r="R9" t="n">
-        <v>7017190</v>
+        <v>7017186</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1550,7 +1550,7 @@
         <v>126117428</v>
       </c>
       <c r="B10" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>126117450</v>
       </c>
       <c r="B11" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,32 +1741,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126117442</v>
+        <v>126117431</v>
       </c>
       <c r="B12" t="n">
-        <v>91534</v>
+        <v>4772</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>100299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>605492</v>
+        <v>605393</v>
       </c>
       <c r="R12" t="n">
-        <v>7017148</v>
+        <v>7017189</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1812,6 +1812,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1838,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126117454</v>
+        <v>126117442</v>
       </c>
       <c r="B13" t="n">
-        <v>91234</v>
+        <v>91538</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1849,21 +1854,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1873,10 +1878,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>605372</v>
+        <v>605492</v>
       </c>
       <c r="R13" t="n">
-        <v>7017035</v>
+        <v>7017148</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1935,32 +1940,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126117431</v>
+        <v>126117454</v>
       </c>
       <c r="B14" t="n">
-        <v>4772</v>
+        <v>91238</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100299</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1970,10 +1975,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>605393</v>
+        <v>605372</v>
       </c>
       <c r="R14" t="n">
-        <v>7017189</v>
+        <v>7017035</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2006,11 +2011,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2040,7 +2040,7 @@
         <v>126117445</v>
       </c>
       <c r="B15" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>126117449</v>
       </c>
       <c r="B16" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>126117429</v>
       </c>
       <c r="B17" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>126117427</v>
       </c>
       <c r="B18" t="n">
-        <v>91203</v>
+        <v>91207</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2425,32 +2425,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126117426</v>
+        <v>126117455</v>
       </c>
       <c r="B19" t="n">
-        <v>5196</v>
+        <v>91260</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105930</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2460,10 +2460,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>605393</v>
+        <v>605403</v>
       </c>
       <c r="R19" t="n">
-        <v>7017189</v>
+        <v>7017171</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2496,11 +2496,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2527,32 +2522,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126117455</v>
+        <v>126117426</v>
       </c>
       <c r="B20" t="n">
-        <v>91256</v>
+        <v>5196</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2562,10 +2557,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>605403</v>
+        <v>605393</v>
       </c>
       <c r="R20" t="n">
-        <v>7017171</v>
+        <v>7017189</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2598,6 +2593,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2627,7 +2627,7 @@
         <v>126117457</v>
       </c>
       <c r="B21" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>126117444</v>
       </c>
       <c r="B22" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2818,32 +2818,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126117430</v>
+        <v>126117440</v>
       </c>
       <c r="B23" t="n">
-        <v>91238</v>
+        <v>98370</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>605397</v>
+        <v>605358</v>
       </c>
       <c r="R23" t="n">
-        <v>7017190</v>
+        <v>7017058</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2915,32 +2915,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126117440</v>
+        <v>126117430</v>
       </c>
       <c r="B24" t="n">
-        <v>98366</v>
+        <v>91242</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>605358</v>
+        <v>605397</v>
       </c>
       <c r="R24" t="n">
-        <v>7017058</v>
+        <v>7017190</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3015,7 +3015,7 @@
         <v>126117451</v>
       </c>
       <c r="B25" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 22209-2025 artfynd.xlsx
+++ b/artfynd/A 22209-2025 artfynd.xlsx
@@ -2818,32 +2818,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126117440</v>
+        <v>126117430</v>
       </c>
       <c r="B23" t="n">
-        <v>98370</v>
+        <v>91242</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>605358</v>
+        <v>605397</v>
       </c>
       <c r="R23" t="n">
-        <v>7017058</v>
+        <v>7017190</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2915,32 +2915,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126117430</v>
+        <v>126117440</v>
       </c>
       <c r="B24" t="n">
-        <v>91242</v>
+        <v>98370</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>605397</v>
+        <v>605358</v>
       </c>
       <c r="R24" t="n">
-        <v>7017190</v>
+        <v>7017058</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>

--- a/artfynd/A 22209-2025 artfynd.xlsx
+++ b/artfynd/A 22209-2025 artfynd.xlsx
@@ -1154,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126117456</v>
+        <v>126117443</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>91538</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,21 +1165,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>605356</v>
+        <v>605449</v>
       </c>
       <c r="R6" t="n">
-        <v>7017178</v>
+        <v>7017035</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1225,11 +1225,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126117443</v>
+        <v>126117456</v>
       </c>
       <c r="B7" t="n">
-        <v>91538</v>
+        <v>78977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,21 +1262,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1291,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>605449</v>
+        <v>605356</v>
       </c>
       <c r="R7" t="n">
-        <v>7017035</v>
+        <v>7017178</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1327,6 +1322,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1453,7 +1453,7 @@
         <v>126117452</v>
       </c>
       <c r="B9" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>126117450</v>
       </c>
       <c r="B11" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>126117449</v>
       </c>
       <c r="B16" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>126117440</v>
       </c>
       <c r="B24" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>126117451</v>
       </c>
       <c r="B25" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 22209-2025 artfynd.xlsx
+++ b/artfynd/A 22209-2025 artfynd.xlsx
@@ -1741,32 +1741,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126117431</v>
+        <v>126117442</v>
       </c>
       <c r="B12" t="n">
-        <v>4772</v>
+        <v>91538</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100299</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>605393</v>
+        <v>605492</v>
       </c>
       <c r="R12" t="n">
-        <v>7017189</v>
+        <v>7017148</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1812,11 +1812,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1843,10 +1838,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126117442</v>
+        <v>126117454</v>
       </c>
       <c r="B13" t="n">
-        <v>91538</v>
+        <v>91238</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,21 +1849,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1878,10 +1873,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>605492</v>
+        <v>605372</v>
       </c>
       <c r="R13" t="n">
-        <v>7017148</v>
+        <v>7017035</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1940,32 +1935,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126117454</v>
+        <v>126117431</v>
       </c>
       <c r="B14" t="n">
-        <v>91238</v>
+        <v>4772</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>100299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1975,10 +1970,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>605372</v>
+        <v>605393</v>
       </c>
       <c r="R14" t="n">
-        <v>7017035</v>
+        <v>7017189</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2011,6 +2006,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 22209-2025 artfynd.xlsx
+++ b/artfynd/A 22209-2025 artfynd.xlsx
@@ -1157,7 +1157,7 @@
         <v>126117443</v>
       </c>
       <c r="B6" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>126117456</v>
       </c>
       <c r="B7" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,32 +1353,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126117446</v>
+        <v>126117452</v>
       </c>
       <c r="B8" t="n">
-        <v>91538</v>
+        <v>98361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>605337</v>
+        <v>605358</v>
       </c>
       <c r="R8" t="n">
-        <v>7017190</v>
+        <v>7017186</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1450,32 +1450,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126117452</v>
+        <v>126117446</v>
       </c>
       <c r="B9" t="n">
-        <v>98352</v>
+        <v>91541</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>605358</v>
+        <v>605337</v>
       </c>
       <c r="R9" t="n">
-        <v>7017186</v>
+        <v>7017190</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1550,7 +1550,7 @@
         <v>126117428</v>
       </c>
       <c r="B10" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>126117450</v>
       </c>
       <c r="B11" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,32 +1741,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126117442</v>
+        <v>126117431</v>
       </c>
       <c r="B12" t="n">
-        <v>91538</v>
+        <v>4772</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>100299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>605492</v>
+        <v>605393</v>
       </c>
       <c r="R12" t="n">
-        <v>7017148</v>
+        <v>7017189</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1812,6 +1812,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1838,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126117454</v>
+        <v>126117442</v>
       </c>
       <c r="B13" t="n">
-        <v>91238</v>
+        <v>91541</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1849,21 +1854,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1873,10 +1878,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>605372</v>
+        <v>605492</v>
       </c>
       <c r="R13" t="n">
-        <v>7017035</v>
+        <v>7017148</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1935,32 +1940,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126117431</v>
+        <v>126117454</v>
       </c>
       <c r="B14" t="n">
-        <v>4772</v>
+        <v>91241</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100299</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1970,10 +1975,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>605393</v>
+        <v>605372</v>
       </c>
       <c r="R14" t="n">
-        <v>7017189</v>
+        <v>7017035</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2006,11 +2011,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2040,7 +2040,7 @@
         <v>126117445</v>
       </c>
       <c r="B15" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>126117449</v>
       </c>
       <c r="B16" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>126117429</v>
       </c>
       <c r="B17" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>126117427</v>
       </c>
       <c r="B18" t="n">
-        <v>91207</v>
+        <v>91210</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>126117455</v>
       </c>
       <c r="B19" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>126117457</v>
       </c>
       <c r="B21" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>126117444</v>
       </c>
       <c r="B22" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>126117430</v>
       </c>
       <c r="B23" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>126117440</v>
       </c>
       <c r="B24" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>126117451</v>
       </c>
       <c r="B25" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 22209-2025 artfynd.xlsx
+++ b/artfynd/A 22209-2025 artfynd.xlsx
@@ -1353,32 +1353,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126117452</v>
+        <v>126117446</v>
       </c>
       <c r="B8" t="n">
-        <v>98361</v>
+        <v>91541</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>605358</v>
+        <v>605337</v>
       </c>
       <c r="R8" t="n">
-        <v>7017186</v>
+        <v>7017190</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1450,32 +1450,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126117446</v>
+        <v>126117452</v>
       </c>
       <c r="B9" t="n">
-        <v>91541</v>
+        <v>98361</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>605337</v>
+        <v>605358</v>
       </c>
       <c r="R9" t="n">
-        <v>7017190</v>
+        <v>7017186</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1741,32 +1741,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126117431</v>
+        <v>126117442</v>
       </c>
       <c r="B12" t="n">
-        <v>4772</v>
+        <v>91541</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100299</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>605393</v>
+        <v>605492</v>
       </c>
       <c r="R12" t="n">
-        <v>7017189</v>
+        <v>7017148</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1812,11 +1812,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1843,10 +1838,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126117442</v>
+        <v>126117454</v>
       </c>
       <c r="B13" t="n">
-        <v>91541</v>
+        <v>91241</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,21 +1849,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1878,10 +1873,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>605492</v>
+        <v>605372</v>
       </c>
       <c r="R13" t="n">
-        <v>7017148</v>
+        <v>7017035</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1940,32 +1935,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126117454</v>
+        <v>126117431</v>
       </c>
       <c r="B14" t="n">
-        <v>91241</v>
+        <v>4772</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>100299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1975,10 +1970,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>605372</v>
+        <v>605393</v>
       </c>
       <c r="R14" t="n">
-        <v>7017035</v>
+        <v>7017189</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2011,6 +2006,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2721,32 +2721,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126117444</v>
+        <v>126117440</v>
       </c>
       <c r="B22" t="n">
-        <v>91541</v>
+        <v>98382</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>605225</v>
+        <v>605358</v>
       </c>
       <c r="R22" t="n">
-        <v>7017164</v>
+        <v>7017058</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2818,10 +2818,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126117430</v>
+        <v>126117444</v>
       </c>
       <c r="B23" t="n">
-        <v>91245</v>
+        <v>91541</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2829,21 +2829,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>605397</v>
+        <v>605225</v>
       </c>
       <c r="R23" t="n">
-        <v>7017190</v>
+        <v>7017164</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2915,32 +2915,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126117440</v>
+        <v>126117430</v>
       </c>
       <c r="B24" t="n">
-        <v>98382</v>
+        <v>91245</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>605358</v>
+        <v>605397</v>
       </c>
       <c r="R24" t="n">
-        <v>7017058</v>
+        <v>7017190</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>

--- a/artfynd/A 22209-2025 artfynd.xlsx
+++ b/artfynd/A 22209-2025 artfynd.xlsx
@@ -1154,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126117443</v>
+        <v>126117456</v>
       </c>
       <c r="B6" t="n">
-        <v>91541</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,21 +1165,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>605449</v>
+        <v>605356</v>
       </c>
       <c r="R6" t="n">
-        <v>7017035</v>
+        <v>7017178</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1225,6 +1225,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126117456</v>
+        <v>126117443</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>91541</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,21 +1267,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1286,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>605356</v>
+        <v>605449</v>
       </c>
       <c r="R7" t="n">
-        <v>7017178</v>
+        <v>7017035</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1322,11 +1327,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2721,32 +2721,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126117440</v>
+        <v>126117444</v>
       </c>
       <c r="B22" t="n">
-        <v>98382</v>
+        <v>91541</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>605358</v>
+        <v>605225</v>
       </c>
       <c r="R22" t="n">
-        <v>7017058</v>
+        <v>7017164</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2818,10 +2818,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126117444</v>
+        <v>126117430</v>
       </c>
       <c r="B23" t="n">
-        <v>91541</v>
+        <v>91245</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2829,21 +2829,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>605225</v>
+        <v>605397</v>
       </c>
       <c r="R23" t="n">
-        <v>7017164</v>
+        <v>7017190</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2915,32 +2915,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126117430</v>
+        <v>126117440</v>
       </c>
       <c r="B24" t="n">
-        <v>91245</v>
+        <v>98382</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>605397</v>
+        <v>605358</v>
       </c>
       <c r="R24" t="n">
-        <v>7017190</v>
+        <v>7017058</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>

--- a/artfynd/A 22209-2025 artfynd.xlsx
+++ b/artfynd/A 22209-2025 artfynd.xlsx
@@ -1154,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126117456</v>
+        <v>126117443</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>91541</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,21 +1165,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>605356</v>
+        <v>605449</v>
       </c>
       <c r="R6" t="n">
-        <v>7017178</v>
+        <v>7017035</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1225,11 +1225,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126117443</v>
+        <v>126117456</v>
       </c>
       <c r="B7" t="n">
-        <v>91541</v>
+        <v>78980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,21 +1262,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1291,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>605449</v>
+        <v>605356</v>
       </c>
       <c r="R7" t="n">
-        <v>7017035</v>
+        <v>7017178</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1327,6 +1322,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,32 +1353,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126117446</v>
+        <v>126117452</v>
       </c>
       <c r="B8" t="n">
-        <v>91541</v>
+        <v>98361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>605337</v>
+        <v>605358</v>
       </c>
       <c r="R8" t="n">
-        <v>7017190</v>
+        <v>7017186</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1450,32 +1450,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126117452</v>
+        <v>126117446</v>
       </c>
       <c r="B9" t="n">
-        <v>98361</v>
+        <v>91541</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>605358</v>
+        <v>605337</v>
       </c>
       <c r="R9" t="n">
-        <v>7017186</v>
+        <v>7017190</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -2721,32 +2721,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126117444</v>
+        <v>126117440</v>
       </c>
       <c r="B22" t="n">
-        <v>91541</v>
+        <v>98382</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>605225</v>
+        <v>605358</v>
       </c>
       <c r="R22" t="n">
-        <v>7017164</v>
+        <v>7017058</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2818,10 +2818,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126117430</v>
+        <v>126117444</v>
       </c>
       <c r="B23" t="n">
-        <v>91245</v>
+        <v>91541</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2829,21 +2829,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>605397</v>
+        <v>605225</v>
       </c>
       <c r="R23" t="n">
-        <v>7017190</v>
+        <v>7017164</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2915,32 +2915,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126117440</v>
+        <v>126117430</v>
       </c>
       <c r="B24" t="n">
-        <v>98382</v>
+        <v>91245</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>605358</v>
+        <v>605397</v>
       </c>
       <c r="R24" t="n">
-        <v>7017058</v>
+        <v>7017190</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>

--- a/artfynd/A 22209-2025 artfynd.xlsx
+++ b/artfynd/A 22209-2025 artfynd.xlsx
@@ -1741,32 +1741,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126117442</v>
+        <v>126117431</v>
       </c>
       <c r="B12" t="n">
-        <v>91541</v>
+        <v>4772</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>100299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>605492</v>
+        <v>605393</v>
       </c>
       <c r="R12" t="n">
-        <v>7017148</v>
+        <v>7017189</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1812,6 +1812,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1838,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126117454</v>
+        <v>126117442</v>
       </c>
       <c r="B13" t="n">
-        <v>91241</v>
+        <v>91541</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1849,21 +1854,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1873,10 +1878,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>605372</v>
+        <v>605492</v>
       </c>
       <c r="R13" t="n">
-        <v>7017035</v>
+        <v>7017148</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1935,32 +1940,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126117431</v>
+        <v>126117454</v>
       </c>
       <c r="B14" t="n">
-        <v>4772</v>
+        <v>91241</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100299</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1970,10 +1975,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>605393</v>
+        <v>605372</v>
       </c>
       <c r="R14" t="n">
-        <v>7017189</v>
+        <v>7017035</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2006,11 +2011,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 22209-2025 artfynd.xlsx
+++ b/artfynd/A 22209-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80851100</v>
+        <v>126117442</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bodberget, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>605512.9766533432</v>
+        <v>605492</v>
       </c>
       <c r="R2" t="n">
-        <v>7017188.058041386</v>
+        <v>7017148</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-10-30</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-10-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,34 +754,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>82237772</v>
+        <v>126117443</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,40 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Forsmo, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>605476.872218895</v>
+        <v>605449</v>
       </c>
       <c r="R3" t="n">
-        <v>7017050.811042666</v>
+        <v>7017035</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-11-29</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-11-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,80 +851,66 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>sofia nordin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>sofia nordin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>82237771</v>
+        <v>126117444</v>
       </c>
       <c r="B4" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1205</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Forsmo, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>605368.7935065922</v>
+        <v>605225</v>
       </c>
       <c r="R4" t="n">
-        <v>7017086.017316403</v>
+        <v>7017164</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-11-30</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-11-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,77 +948,63 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>sofia nordin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>sofia nordin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>82237773</v>
+        <v>126117445</v>
       </c>
       <c r="B5" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Forsmo, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>605591.9138357369</v>
+        <v>605242</v>
       </c>
       <c r="R5" t="n">
-        <v>7017050.979499015</v>
+        <v>7017164</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1106,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-11-28</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-11-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,34 +1045,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>sofia nordin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>sofia nordin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126117443</v>
+        <v>126117446</v>
       </c>
       <c r="B6" t="n">
-        <v>91541</v>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,12 +1083,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1189,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>605449</v>
+        <v>605337</v>
       </c>
       <c r="R6" t="n">
-        <v>7017035</v>
+        <v>7017190</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1251,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126117456</v>
+        <v>126117454</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1286,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>605356</v>
+        <v>605372</v>
       </c>
       <c r="R7" t="n">
-        <v>7017178</v>
+        <v>7017035</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1322,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126117446</v>
+        <v>126117428</v>
       </c>
       <c r="B8" t="n">
-        <v>91541</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>605337</v>
+        <v>605442</v>
       </c>
       <c r="R8" t="n">
-        <v>7017190</v>
+        <v>7017113</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1450,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126117452</v>
+        <v>126117429</v>
       </c>
       <c r="B9" t="n">
-        <v>98361</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1485,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>605358</v>
+        <v>605445</v>
       </c>
       <c r="R9" t="n">
-        <v>7017186</v>
+        <v>7017046</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1547,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126117428</v>
+        <v>126117430</v>
       </c>
       <c r="B10" t="n">
-        <v>91245</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>605442</v>
+        <v>605397</v>
       </c>
       <c r="R10" t="n">
-        <v>7017113</v>
+        <v>7017190</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1644,48 +1548,51 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126117450</v>
+        <v>82237771</v>
       </c>
       <c r="B11" t="n">
-        <v>98361</v>
+        <v>91920</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Forsmo, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>605356</v>
+        <v>605369</v>
       </c>
       <c r="R11" t="n">
-        <v>7017183</v>
+        <v>7017086</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1709,12 +1616,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2019-11-30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2019-11-30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1723,63 +1630,72 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>sofia nordin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>sofia nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126117442</v>
+        <v>82237773</v>
       </c>
       <c r="B12" t="n">
-        <v>91541</v>
+        <v>91920</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1205</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Forsmo, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>605492</v>
+        <v>605592</v>
       </c>
       <c r="R12" t="n">
-        <v>7017148</v>
+        <v>7017051</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1806,12 +1722,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2019-11-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2019-11-28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1820,50 +1736,56 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>sofia nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>sofia nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126117454</v>
+        <v>126117427</v>
       </c>
       <c r="B13" t="n">
-        <v>91241</v>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1873,10 +1795,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>605372</v>
+        <v>605225</v>
       </c>
       <c r="R13" t="n">
-        <v>7017035</v>
+        <v>7017157</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1935,45 +1857,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126117431</v>
+        <v>80851100</v>
       </c>
       <c r="B14" t="n">
-        <v>4772</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Bodberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>605393</v>
+        <v>605513</v>
       </c>
       <c r="R14" t="n">
-        <v>7017189</v>
+        <v>7017188</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2000,17 +1925,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2019-10-30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>2019-10-30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2019,50 +1939,51 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126117445</v>
+        <v>126117456</v>
       </c>
       <c r="B15" t="n">
-        <v>91541</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2072,10 +1993,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>605242</v>
+        <v>605356</v>
       </c>
       <c r="R15" t="n">
-        <v>7017164</v>
+        <v>7017178</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2108,6 +2029,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2134,10 +2060,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126117449</v>
+        <v>126117457</v>
       </c>
       <c r="B16" t="n">
-        <v>98361</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2145,21 +2071,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2169,10 +2095,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>605348</v>
+        <v>605367</v>
       </c>
       <c r="R16" t="n">
-        <v>7017068</v>
+        <v>7017177</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2231,10 +2157,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126117429</v>
+        <v>82237772</v>
       </c>
       <c r="B17" t="n">
-        <v>91245</v>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2242,37 +2168,40 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Forsmo, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>605445</v>
+        <v>605477</v>
       </c>
       <c r="R17" t="n">
-        <v>7017046</v>
+        <v>7017051</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2296,12 +2225,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2019-11-29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2019-11-29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2310,28 +2239,34 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>sofia nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>sofia nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126117427</v>
+        <v>126117431</v>
       </c>
       <c r="B18" t="n">
-        <v>91210</v>
+        <v>4775</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2339,21 +2274,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2363,10 +2298,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>605225</v>
+        <v>605393</v>
       </c>
       <c r="R18" t="n">
-        <v>7017157</v>
+        <v>7017189</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2399,6 +2334,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2425,32 +2365,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126117455</v>
+        <v>126117460</v>
       </c>
       <c r="B19" t="n">
-        <v>91263</v>
+        <v>5179</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2460,10 +2400,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>605403</v>
+        <v>605391</v>
       </c>
       <c r="R19" t="n">
-        <v>7017171</v>
+        <v>7017189</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2496,6 +2436,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2525,7 +2470,7 @@
         <v>126117426</v>
       </c>
       <c r="B20" t="n">
-        <v>5196</v>
+        <v>5199</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2624,32 +2569,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126117457</v>
+        <v>126117449</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2659,10 +2604,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>605367</v>
+        <v>605348</v>
       </c>
       <c r="R21" t="n">
-        <v>7017177</v>
+        <v>7017068</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2721,32 +2666,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126117440</v>
+        <v>126117450</v>
       </c>
       <c r="B22" t="n">
-        <v>98382</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2756,10 +2701,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>605358</v>
+        <v>605356</v>
       </c>
       <c r="R22" t="n">
-        <v>7017058</v>
+        <v>7017183</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2818,32 +2763,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126117444</v>
+        <v>126117451</v>
       </c>
       <c r="B23" t="n">
-        <v>91541</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2853,10 +2798,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>605225</v>
+        <v>605345</v>
       </c>
       <c r="R23" t="n">
-        <v>7017164</v>
+        <v>7017186</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2915,32 +2860,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126117430</v>
+        <v>126117452</v>
       </c>
       <c r="B24" t="n">
-        <v>91245</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2950,10 +2895,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>605397</v>
+        <v>605358</v>
       </c>
       <c r="R24" t="n">
-        <v>7017190</v>
+        <v>7017186</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3012,32 +2957,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126117451</v>
+        <v>126117440</v>
       </c>
       <c r="B25" t="n">
-        <v>98361</v>
+        <v>99140</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3047,10 +2992,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>605345</v>
+        <v>605358</v>
       </c>
       <c r="R25" t="n">
-        <v>7017186</v>
+        <v>7017058</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3106,108 +3051,6 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>126117460</v>
-      </c>
-      <c r="B26" t="n">
-        <v>5176</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Callidium coriaceum</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Sollefteå, Ång</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>605391</v>
-      </c>
-      <c r="R26" t="n">
-        <v>7017189</v>
-      </c>
-      <c r="S26" t="n">
-        <v>25</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Ed</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22209-2025 artfynd.xlsx
+++ b/artfynd/A 22209-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117442</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117443</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117444</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117445</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117446</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117454</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117428</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117429</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117430</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1651,6 +1701,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82237771</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1757,6 +1812,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82237773</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1854,6 +1914,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117427</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1955,6 +2020,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80851100</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2057,6 +2127,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117456</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2154,6 +2229,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117457</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2260,6 +2340,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82237772</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2362,6 +2447,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117431</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2464,6 +2554,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117460</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2566,6 +2661,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117426</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2663,6 +2763,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117449</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2760,6 +2865,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117450</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2857,6 +2967,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117451</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2954,6 +3069,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117452</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3051,8 +3171,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117440</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>